--- a/outputs/Block2_2026_Target_Stability_v12.xlsx
+++ b/outputs/Block2_2026_Target_Stability_v12.xlsx
@@ -88,6 +88,9 @@
     <t>D House Seats LOST</t>
   </si>
   <si>
+    <t>RHouLeanResLD  (&gt;1&lt;=5%)</t>
+  </si>
+  <si>
     <t>D Senate After</t>
   </si>
   <si>
@@ -100,9 +103,6 @@
     <t>R Senate After</t>
   </si>
   <si>
-    <t>RHouLeanResLD  (&gt;1&lt;=5%)</t>
-  </si>
-  <si>
     <t>RHouLikResH (&gt;5%&lt;=10%)</t>
   </si>
   <si>
@@ -112,15 +112,15 @@
     <t>DHouLeanResH  (&gt;1&lt;=5%)</t>
   </si>
   <si>
+    <t>DHouLikResLR (&gt;5%&lt;=10%)</t>
+  </si>
+  <si>
     <t>RHouLikResLD (&gt;5%&lt;=10%)</t>
   </si>
   <si>
     <t>DHouLeanResLR  (&gt;1&lt;=5%)</t>
   </si>
   <si>
-    <t>DHouLikResLR (&gt;5%&lt;=10%)</t>
-  </si>
-  <si>
     <t>DSenSafResH (&gt;10%)</t>
   </si>
   <si>
@@ -136,61 +136,61 @@
     <t>RHouSafResLD (&gt;10%)</t>
   </si>
   <si>
+    <t>RHouTiltResLD (&lt;=1%)</t>
+  </si>
+  <si>
+    <t>DHouTiltResLR (&lt;=1%)</t>
+  </si>
+  <si>
+    <t>DSenLeanResH  (&gt;1&lt;=5%)</t>
+  </si>
+  <si>
+    <t>DSenLeanResLR  (&gt;1&lt;=5%)</t>
+  </si>
+  <si>
+    <t>DSenLikResH (&gt;5%&lt;=10%)</t>
+  </si>
+  <si>
+    <t>DSenLikResLR (&gt;5%&lt;=10%)</t>
+  </si>
+  <si>
+    <t>DSenTiltResH (&lt;=1%)</t>
+  </si>
+  <si>
+    <t>RHouTiltResH (&lt;=1%)</t>
+  </si>
+  <si>
+    <t>RSenLikResH (&gt;5%&lt;=10%)</t>
+  </si>
+  <si>
+    <t>RSenLikResLD (&gt;5%&lt;=10%)</t>
+  </si>
+  <si>
+    <t>RSenSafResH (&gt;10%)</t>
+  </si>
+  <si>
+    <t>RSenSafResLD (&gt;10%)</t>
+  </si>
+  <si>
+    <t>RSenTiltResH (&lt;=1%)</t>
+  </si>
+  <si>
+    <t>RSenTiltResLD (&lt;=1%)</t>
+  </si>
+  <si>
+    <t>DPP</t>
+  </si>
+  <si>
+    <t>RPP</t>
+  </si>
+  <si>
     <t>DHouTiltResH (&lt;=1%)</t>
   </si>
   <si>
-    <t>DHouTiltResLR (&lt;=1%)</t>
-  </si>
-  <si>
-    <t>DSenLeanResLR  (&gt;1&lt;=5%)</t>
-  </si>
-  <si>
-    <t>DSenLikResH (&gt;5%&lt;=10%)</t>
-  </si>
-  <si>
-    <t>DSenLikResLR (&gt;5%&lt;=10%)</t>
-  </si>
-  <si>
-    <t>DSenTiltResH (&lt;=1%)</t>
-  </si>
-  <si>
-    <t>RHouTiltResH (&lt;=1%)</t>
-  </si>
-  <si>
-    <t>RHouTiltResLD (&lt;=1%)</t>
+    <t>DSenTiltResLR (&lt;=1%)</t>
   </si>
   <si>
     <t>RSenLeanResH  (&gt;1&lt;=5%)</t>
-  </si>
-  <si>
-    <t>RSenLikResH (&gt;5%&lt;=10%)</t>
-  </si>
-  <si>
-    <t>RSenLikResLD (&gt;5%&lt;=10%)</t>
-  </si>
-  <si>
-    <t>RSenSafResH (&gt;10%)</t>
-  </si>
-  <si>
-    <t>RSenSafResLD (&gt;10%)</t>
-  </si>
-  <si>
-    <t>RSenTiltResH (&lt;=1%)</t>
-  </si>
-  <si>
-    <t>RSenTiltResLD (&lt;=1%)</t>
-  </si>
-  <si>
-    <t>DPP</t>
-  </si>
-  <si>
-    <t>RPP</t>
-  </si>
-  <si>
-    <t>DSenLeanResH  (&gt;1&lt;=5%)</t>
-  </si>
-  <si>
-    <t>DSenTiltResLR (&lt;=1%)</t>
   </si>
   <si>
     <t>RSenLeanResLD  (&gt;1&lt;=5%)</t>
@@ -654,25 +654,25 @@
         <v>66</v>
       </c>
       <c r="E2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F2">
-        <v>174.8</v>
+        <v>173.2</v>
       </c>
       <c r="G2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H2">
-        <v>0.8000000000000114</v>
+        <v>1.199999999999989</v>
       </c>
       <c r="I2">
-        <v>9.338094023943002</v>
+        <v>9.471008394041261</v>
       </c>
       <c r="J2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="K2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="L2">
         <v>25</v>
@@ -710,28 +710,28 @@
         <v>66</v>
       </c>
       <c r="E3">
+        <v>223</v>
+      </c>
+      <c r="F3">
+        <v>220.6</v>
+      </c>
+      <c r="G3">
         <v>219</v>
       </c>
-      <c r="F3">
-        <v>218</v>
-      </c>
-      <c r="G3">
-        <v>217</v>
-      </c>
       <c r="H3">
-        <v>-1</v>
+        <v>-2.400000000000006</v>
       </c>
       <c r="I3">
-        <v>9.273618495495704</v>
+        <v>10.11434624679223</v>
       </c>
       <c r="J3">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="K3">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="L3">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M3">
         <v>14</v>
@@ -766,28 +766,28 @@
         <v>66</v>
       </c>
       <c r="E4">
+        <v>212</v>
+      </c>
+      <c r="F4">
+        <v>214.4</v>
+      </c>
+      <c r="G4">
         <v>216</v>
       </c>
-      <c r="F4">
-        <v>217</v>
-      </c>
-      <c r="G4">
-        <v>218</v>
-      </c>
       <c r="H4">
-        <v>1</v>
+        <v>2.400000000000006</v>
       </c>
       <c r="I4">
-        <v>9.273618495495704</v>
+        <v>10.11434624679223</v>
       </c>
       <c r="J4">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="K4">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L4">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M4">
         <v>14</v>
@@ -822,28 +822,28 @@
         <v>66</v>
       </c>
       <c r="E5">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F5">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G5">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>7.176350047203662</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K5">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="L5">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M5">
         <v>10</v>
@@ -878,13 +878,13 @@
         <v>66</v>
       </c>
       <c r="E6">
+        <v>16</v>
+      </c>
+      <c r="F6">
+        <v>16</v>
+      </c>
+      <c r="G6">
         <v>15</v>
-      </c>
-      <c r="F6">
-        <v>15</v>
-      </c>
-      <c r="G6">
-        <v>14</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -893,10 +893,10 @@
         <v>6.442049363362563</v>
       </c>
       <c r="J6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L6">
         <v>16</v>
@@ -934,37 +934,37 @@
         <v>66</v>
       </c>
       <c r="E7">
+        <v>8</v>
+      </c>
+      <c r="F7">
+        <v>10.4</v>
+      </c>
+      <c r="G7">
         <v>11</v>
       </c>
-      <c r="F7">
+      <c r="H7">
+        <v>2.4</v>
+      </c>
+      <c r="I7">
+        <v>4.929503017546495</v>
+      </c>
+      <c r="J7">
+        <v>4</v>
+      </c>
+      <c r="K7">
+        <v>16</v>
+      </c>
+      <c r="L7">
         <v>12</v>
       </c>
-      <c r="G7">
-        <v>13</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>4.358898943540674</v>
-      </c>
-      <c r="J7">
-        <v>7</v>
-      </c>
-      <c r="K7">
-        <v>17</v>
-      </c>
-      <c r="L7">
-        <v>10</v>
-      </c>
       <c r="M7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N7">
         <v>16</v>
       </c>
       <c r="O7">
-        <v>0.375</v>
+        <v>0.5</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
@@ -981,46 +981,46 @@
         <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
         <v>66</v>
       </c>
       <c r="E8">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="F8">
-        <v>48.6</v>
+        <v>5</v>
       </c>
       <c r="G8">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="H8">
-        <v>-1.399999999999999</v>
+        <v>1</v>
       </c>
       <c r="I8">
-        <v>1.816590212458495</v>
+        <v>2.91547594742265</v>
       </c>
       <c r="J8">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="K8">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="L8">
+        <v>7</v>
+      </c>
+      <c r="M8">
         <v>5</v>
       </c>
-      <c r="M8">
-        <v>4</v>
-      </c>
       <c r="N8">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="O8">
-        <v>1.428571428571429</v>
+        <v>1.388888888888889</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
@@ -1037,34 +1037,34 @@
         <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D9" t="s">
         <v>66</v>
       </c>
       <c r="E9">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="F9">
-        <v>17.4</v>
+        <v>48.8</v>
       </c>
       <c r="G9">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="H9">
-        <v>-1.600000000000001</v>
+        <v>-1.200000000000003</v>
       </c>
       <c r="I9">
-        <v>1.949358868961793</v>
+        <v>1.788854381999832</v>
       </c>
       <c r="J9">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="K9">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="L9">
         <v>5</v>
@@ -1073,10 +1073,10 @@
         <v>4</v>
       </c>
       <c r="N9">
-        <v>5.2</v>
+        <v>2.8</v>
       </c>
       <c r="O9">
-        <v>0.7692307692307692</v>
+        <v>1.428571428571429</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
@@ -1102,25 +1102,25 @@
         <v>66</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="F10">
-        <v>2.6</v>
+        <v>17.4</v>
       </c>
       <c r="G10">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H10">
-        <v>1.6</v>
+        <v>-1.600000000000001</v>
       </c>
       <c r="I10">
-        <v>2.509980079602227</v>
+        <v>1.949358868961793</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K10">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="L10">
         <v>5</v>
@@ -1129,10 +1129,10 @@
         <v>4</v>
       </c>
       <c r="N10">
-        <v>8.6</v>
+        <v>5.2</v>
       </c>
       <c r="O10">
-        <v>0.4651162790697674</v>
+        <v>0.7692307692307692</v>
       </c>
       <c r="P10" t="b">
         <v>1</v>
@@ -1149,46 +1149,46 @@
         <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D11" t="s">
         <v>66</v>
       </c>
       <c r="E11">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>51.4</v>
+        <v>2.2</v>
       </c>
       <c r="G11">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="H11">
-        <v>1.399999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="I11">
-        <v>1.816590212458495</v>
+        <v>2.049390153191919</v>
       </c>
       <c r="J11">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="K11">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="L11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M11">
         <v>4</v>
       </c>
       <c r="N11">
-        <v>2.6</v>
+        <v>8.6</v>
       </c>
       <c r="O11">
-        <v>1.538461538461538</v>
+        <v>0.4651162790697674</v>
       </c>
       <c r="P11" t="b">
         <v>1</v>
@@ -1205,46 +1205,46 @@
         <v>28</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D12" t="s">
         <v>66</v>
       </c>
       <c r="E12">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="F12">
-        <v>4.6</v>
+        <v>51.2</v>
       </c>
       <c r="G12">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="H12">
-        <v>0.5999999999999996</v>
+        <v>1.200000000000003</v>
       </c>
       <c r="I12">
-        <v>2.880972058177587</v>
+        <v>1.788854381999832</v>
       </c>
       <c r="J12">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="K12">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="L12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M12">
         <v>4</v>
       </c>
       <c r="N12">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="O12">
-        <v>1.111111111111111</v>
+        <v>1.538461538461538</v>
       </c>
       <c r="P12" t="b">
         <v>1</v>
@@ -1385,16 +1385,16 @@
         <v>10</v>
       </c>
       <c r="F15">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G15">
         <v>10</v>
       </c>
       <c r="H15">
-        <v>-0.5999999999999996</v>
+        <v>-0.8000000000000007</v>
       </c>
       <c r="I15">
-        <v>1.949358868961793</v>
+        <v>2.16794833886788</v>
       </c>
       <c r="J15">
         <v>7</v>
@@ -1438,37 +1438,37 @@
         <v>66</v>
       </c>
       <c r="E16">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F16">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="G16">
+        <v>3</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16">
+        <v>1.870828693386971</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
         <v>4</v>
       </c>
-      <c r="H16">
-        <v>-0.4000000000000004</v>
-      </c>
-      <c r="I16">
-        <v>2.073644135332772</v>
-      </c>
-      <c r="J16">
-        <v>3</v>
-      </c>
-      <c r="K16">
-        <v>8</v>
-      </c>
       <c r="L16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M16">
         <v>3</v>
       </c>
       <c r="N16">
-        <v>3.6</v>
+        <v>6</v>
       </c>
       <c r="O16">
-        <v>0.8333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="P16" t="b">
         <v>1</v>
@@ -1494,37 +1494,37 @@
         <v>66</v>
       </c>
       <c r="E17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F17">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="G17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H17">
-        <v>-0.4000000000000004</v>
+        <v>0</v>
       </c>
       <c r="I17">
-        <v>1.51657508881031</v>
+        <v>2.121320343559642</v>
       </c>
       <c r="J17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L17">
+        <v>5</v>
+      </c>
+      <c r="M17">
         <v>3</v>
       </c>
-      <c r="M17">
-        <v>2</v>
-      </c>
       <c r="N17">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="O17">
-        <v>0.7692307692307692</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="P17" t="b">
         <v>1</v>
@@ -1550,37 +1550,37 @@
         <v>66</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F18">
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
       <c r="G18">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H18">
-        <v>0.2000000000000002</v>
+        <v>-0.2000000000000002</v>
       </c>
       <c r="I18">
         <v>1.643167672515498</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K18">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M18">
         <v>2</v>
       </c>
       <c r="N18">
-        <v>6</v>
+        <v>2.6</v>
       </c>
       <c r="O18">
-        <v>0.3333333333333333</v>
+        <v>0.7692307692307692</v>
       </c>
       <c r="P18" t="b">
         <v>1</v>
@@ -1609,16 +1609,16 @@
         <v>10</v>
       </c>
       <c r="F19">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="G19">
         <v>9</v>
       </c>
       <c r="H19">
-        <v>-1.199999999999999</v>
+        <v>-1</v>
       </c>
       <c r="I19">
-        <v>0.8366600265340756</v>
+        <v>0.7071067811865476</v>
       </c>
       <c r="J19">
         <v>8</v>
@@ -1721,25 +1721,25 @@
         <v>3</v>
       </c>
       <c r="F21">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="G21">
         <v>3</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>0.2000000000000002</v>
       </c>
       <c r="I21">
-        <v>1.224744871391589</v>
+        <v>1.483239697419133</v>
       </c>
       <c r="J21">
         <v>1</v>
       </c>
       <c r="K21">
+        <v>5</v>
+      </c>
+      <c r="L21">
         <v>4</v>
-      </c>
-      <c r="L21">
-        <v>3</v>
       </c>
       <c r="M21">
         <v>2</v>
@@ -1777,22 +1777,22 @@
         <v>13</v>
       </c>
       <c r="F22">
-        <v>12.4</v>
+        <v>13</v>
       </c>
       <c r="G22">
         <v>12</v>
       </c>
       <c r="H22">
-        <v>-0.5999999999999996</v>
+        <v>0</v>
       </c>
       <c r="I22">
-        <v>1.140175425099138</v>
+        <v>1.414213562373095</v>
       </c>
       <c r="J22">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K22">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L22">
         <v>3</v>
@@ -1886,37 +1886,37 @@
         <v>66</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F24">
+        <v>2.2</v>
+      </c>
+      <c r="G24">
+        <v>2</v>
+      </c>
+      <c r="H24">
+        <v>-0.7999999999999998</v>
+      </c>
+      <c r="I24">
+        <v>0.8366600265340756</v>
+      </c>
+      <c r="J24">
+        <v>1</v>
+      </c>
+      <c r="K24">
+        <v>3</v>
+      </c>
+      <c r="L24">
+        <v>2</v>
+      </c>
+      <c r="M24">
+        <v>2</v>
+      </c>
+      <c r="N24">
         <v>1.2</v>
       </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-      <c r="H24">
-        <v>0.2</v>
-      </c>
-      <c r="I24">
-        <v>0.4472135954999579</v>
-      </c>
-      <c r="J24">
-        <v>1</v>
-      </c>
-      <c r="K24">
-        <v>2</v>
-      </c>
-      <c r="L24">
-        <v>1</v>
-      </c>
-      <c r="M24">
-        <v>1</v>
-      </c>
-      <c r="N24">
-        <v>0.8</v>
-      </c>
       <c r="O24">
-        <v>1.25</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="P24" t="b">
         <v>1</v>
@@ -1945,13 +1945,13 @@
         <v>2</v>
       </c>
       <c r="F25">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="G25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H25">
-        <v>-0.3999999999999999</v>
+        <v>-0.6000000000000001</v>
       </c>
       <c r="I25">
         <v>0.5477225575051661</v>
@@ -1998,19 +1998,19 @@
         <v>66</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26">
-        <v>0.4</v>
+        <v>-0.2</v>
       </c>
       <c r="I26">
-        <v>0.5477225575051662</v>
+        <v>0.4472135954999579</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -2025,10 +2025,10 @@
         <v>1</v>
       </c>
       <c r="N26">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="O26">
-        <v>0.625</v>
+        <v>1.25</v>
       </c>
       <c r="P26" t="b">
         <v>1</v>
@@ -2054,25 +2054,25 @@
         <v>66</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="G27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="I27">
-        <v>0.4472135954999579</v>
+        <v>0.5477225575051662</v>
       </c>
       <c r="J27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L27">
         <v>1</v>
@@ -2081,10 +2081,10 @@
         <v>1</v>
       </c>
       <c r="N27">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="O27">
-        <v>1.25</v>
+        <v>0.625</v>
       </c>
       <c r="P27" t="b">
         <v>1</v>
@@ -2110,25 +2110,25 @@
         <v>66</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28">
         <v>0.2</v>
       </c>
       <c r="I28">
-        <v>0.447213595499958</v>
+        <v>0.4472135954999579</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L28">
         <v>1</v>
@@ -2137,10 +2137,10 @@
         <v>1</v>
       </c>
       <c r="N28">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="O28">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="P28" t="b">
         <v>1</v>
@@ -2166,19 +2166,19 @@
         <v>66</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F29">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29">
-        <v>-0.4</v>
+        <v>0.2</v>
       </c>
       <c r="I29">
-        <v>0.5477225575051662</v>
+        <v>0.447213595499958</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -2193,10 +2193,10 @@
         <v>1</v>
       </c>
       <c r="N29">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="O29">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
       <c r="P29" t="b">
         <v>1</v>
@@ -2213,7 +2213,7 @@
         <v>46</v>
       </c>
       <c r="B30" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C30" t="s">
         <v>64</v>
@@ -2222,25 +2222,25 @@
         <v>66</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F30">
-        <v>3.2</v>
+        <v>0.6</v>
       </c>
       <c r="G30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H30">
-        <v>0.2000000000000002</v>
+        <v>-0.4</v>
       </c>
       <c r="I30">
-        <v>0.4472135954999579</v>
+        <v>0.5477225575051662</v>
       </c>
       <c r="J30">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K30">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L30">
         <v>1</v>
@@ -2249,10 +2249,10 @@
         <v>1</v>
       </c>
       <c r="N30">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="O30">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="P30" t="b">
         <v>1</v>
@@ -2278,37 +2278,37 @@
         <v>66</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F31">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="G31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>-0.7999999999999998</v>
       </c>
       <c r="I31">
-        <v>0.7071067811865476</v>
+        <v>0.4472135954999579</v>
       </c>
       <c r="J31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M31">
         <v>1</v>
       </c>
       <c r="N31">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="O31">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
       <c r="P31" t="b">
         <v>1</v>
@@ -2334,34 +2334,37 @@
         <v>66</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="G32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H32">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I32">
-        <v>0.4472135954999579</v>
+        <v>0.7071067811865476</v>
       </c>
       <c r="J32">
         <v>1</v>
       </c>
       <c r="K32">
+        <v>3</v>
+      </c>
+      <c r="L32">
         <v>2</v>
       </c>
-      <c r="L32">
-        <v>1</v>
-      </c>
       <c r="M32">
         <v>1</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>0.6</v>
+      </c>
+      <c r="O32">
+        <v>1.666666666666667</v>
       </c>
       <c r="P32" t="b">
         <v>1</v>
@@ -2387,37 +2390,37 @@
         <v>66</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F33">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="G33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="I33">
-        <v>0.7071067811865476</v>
+        <v>0.5477225575051662</v>
       </c>
       <c r="J33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M33">
         <v>1</v>
       </c>
       <c r="N33">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="O33">
-        <v>1.666666666666667</v>
+        <v>2.5</v>
       </c>
       <c r="P33" t="b">
         <v>1</v>
@@ -2443,37 +2446,37 @@
         <v>66</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F34">
-        <v>0.4</v>
+        <v>15.2</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H34">
-        <v>0.4</v>
+        <v>0.1999999999999993</v>
       </c>
       <c r="I34">
-        <v>0.5477225575051662</v>
+        <v>0.8366600265340756</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K34">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="L34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M34">
         <v>1</v>
       </c>
       <c r="N34">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="O34">
-        <v>2.5</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="P34" t="b">
         <v>1</v>
@@ -2499,37 +2502,37 @@
         <v>66</v>
       </c>
       <c r="E35">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F35">
-        <v>15.4</v>
+        <v>0.8</v>
       </c>
       <c r="G35">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H35">
-        <v>0.4000000000000004</v>
+        <v>-0.2</v>
       </c>
       <c r="I35">
-        <v>0.8944271909999159</v>
+        <v>0.447213595499958</v>
       </c>
       <c r="J35">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K35">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="L35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M35">
         <v>1</v>
       </c>
       <c r="N35">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="O35">
-        <v>0.8333333333333334</v>
+        <v>2.5</v>
       </c>
       <c r="P35" t="b">
         <v>1</v>
@@ -2558,16 +2561,16 @@
         <v>1</v>
       </c>
       <c r="F36">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G36">
         <v>1</v>
       </c>
       <c r="H36">
-        <v>-0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="I36">
-        <v>0.447213595499958</v>
+        <v>0.5477225575051662</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -2614,34 +2617,34 @@
         <v>1</v>
       </c>
       <c r="F37">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
       <c r="I37">
-        <v>0.5477225575051662</v>
+        <v>0.7071067811865476</v>
       </c>
       <c r="J37">
         <v>0</v>
       </c>
       <c r="K37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M37">
         <v>1</v>
       </c>
       <c r="N37">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="O37">
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
       <c r="P37" t="b">
         <v>1</v>
@@ -2658,46 +2661,46 @@
         <v>54</v>
       </c>
       <c r="B38" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C38" t="s">
         <v>64</v>
       </c>
       <c r="D38" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E38">
-        <v>1</v>
+        <v>52.35678365171034</v>
       </c>
       <c r="F38">
-        <v>0.8</v>
+        <v>52.35678365171036</v>
       </c>
       <c r="G38">
-        <v>1</v>
+        <v>52.40801865837405</v>
       </c>
       <c r="H38">
-        <v>-0.2</v>
+        <v>1.4210854715202E-14</v>
       </c>
       <c r="I38">
-        <v>0.447213595499958</v>
+        <v>0.09311987620122464</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>52.20577521101733</v>
       </c>
       <c r="K38">
-        <v>1</v>
+        <v>52.42150155486451</v>
       </c>
       <c r="L38">
-        <v>1</v>
+        <v>0.2157263438471801</v>
       </c>
       <c r="M38">
-        <v>1</v>
+        <v>0.1510084406930119</v>
       </c>
       <c r="N38">
-        <v>0.8</v>
+        <v>1.323492690170848</v>
       </c>
       <c r="O38">
-        <v>1.25</v>
+        <v>0.1140984319856866</v>
       </c>
       <c r="P38" t="b">
         <v>1</v>
@@ -2723,37 +2726,37 @@
         <v>67</v>
       </c>
       <c r="E39">
-        <v>52.06818961625282</v>
+        <v>44.72321634828965</v>
       </c>
       <c r="F39">
-        <v>52.06818961625282</v>
+        <v>44.72321634828965</v>
       </c>
       <c r="G39">
-        <v>52.11914221218962</v>
+        <v>44.76698134162594</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>7.105427357601002E-15</v>
       </c>
       <c r="I39">
-        <v>0.09260659331828282</v>
+        <v>0.07954309029709221</v>
       </c>
       <c r="J39">
-        <v>51.91801354401807</v>
+        <v>44.59422478898268</v>
       </c>
       <c r="K39">
-        <v>52.13255079006773</v>
+        <v>44.7784984451355</v>
       </c>
       <c r="L39">
-        <v>0.2145372460496588</v>
+        <v>0.1842736561528184</v>
       </c>
       <c r="M39">
-        <v>0.1501760722347498</v>
+        <v>0.1289915593069679</v>
       </c>
       <c r="N39">
-        <v>1.323492690170848</v>
+        <v>1.064148394560983</v>
       </c>
       <c r="O39">
-        <v>0.1134695139233174</v>
+        <v>0.1212157627322115</v>
       </c>
       <c r="P39" t="b">
         <v>1</v>
@@ -2770,46 +2773,46 @@
         <v>56</v>
       </c>
       <c r="B40" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C40" t="s">
         <v>64</v>
       </c>
       <c r="D40" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E40">
-        <v>45.01181038374718</v>
+        <v>1</v>
       </c>
       <c r="F40">
-        <v>45.01181038374718</v>
+        <v>1</v>
       </c>
       <c r="G40">
-        <v>45.05585778781037</v>
+        <v>1</v>
       </c>
       <c r="H40">
         <v>0</v>
       </c>
       <c r="I40">
-        <v>0.08005637318003306</v>
+        <v>0</v>
       </c>
       <c r="J40">
-        <v>44.88198645598194</v>
+        <v>1</v>
       </c>
       <c r="K40">
-        <v>45.06744920993228</v>
+        <v>1</v>
       </c>
       <c r="L40">
-        <v>0.1854627539503397</v>
+        <v>0</v>
       </c>
       <c r="M40">
-        <v>0.1298239277652371</v>
+        <v>0</v>
       </c>
       <c r="N40">
-        <v>1.064148394560983</v>
+        <v>0.8</v>
       </c>
       <c r="O40">
-        <v>0.121997954823581</v>
+        <v>0</v>
       </c>
       <c r="P40" t="b">
         <v>1</v>
@@ -2835,13 +2838,13 @@
         <v>66</v>
       </c>
       <c r="E41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41">
         <v>0</v>
@@ -2850,10 +2853,10 @@
         <v>0</v>
       </c>
       <c r="J41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -2862,7 +2865,7 @@
         <v>0</v>
       </c>
       <c r="N41">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="O41">
         <v>0</v>
@@ -2891,13 +2894,13 @@
         <v>66</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42">
         <v>0</v>
@@ -2906,10 +2909,10 @@
         <v>0</v>
       </c>
       <c r="J42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -2918,9 +2921,6 @@
         <v>0</v>
       </c>
       <c r="N42">
-        <v>0.2</v>
-      </c>
-      <c r="O42">
         <v>0</v>
       </c>
       <c r="P42" t="b">

--- a/outputs/Block2_2026_Target_Stability_v12.xlsx
+++ b/outputs/Block2_2026_Target_Stability_v12.xlsx
@@ -552,37 +552,37 @@
         <v>32</v>
       </c>
       <c r="E2">
-        <v>52.78010224494333</v>
+        <v>52.77257599289993</v>
       </c>
       <c r="F2">
-        <v>52.78010224494333</v>
+        <v>52.77257599289993</v>
       </c>
       <c r="G2">
-        <v>52.83175150033341</v>
+        <v>52.82421788329265</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.09387277529559609</v>
+        <v>0.09385938937672039</v>
       </c>
       <c r="J2">
-        <v>52.6278728606357</v>
+        <v>52.62036831595296</v>
       </c>
       <c r="K2">
-        <v>52.8453434096466</v>
+        <v>52.83780785444863</v>
       </c>
       <c r="L2">
-        <v>0.2174705490108906</v>
+        <v>0.2174395384956753</v>
       </c>
       <c r="M2">
-        <v>0.1522293843076241</v>
+        <v>0.152207676946972</v>
       </c>
       <c r="N2">
         <v>1.323492690170848</v>
       </c>
       <c r="O2">
-        <v>0.1150209483121309</v>
+        <v>0.1150045467401288</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
@@ -608,37 +608,37 @@
         <v>32</v>
       </c>
       <c r="E3">
-        <v>44.29989775505667</v>
+        <v>44.30742400710007</v>
       </c>
       <c r="F3">
-        <v>44.29989775505668</v>
+        <v>44.30742400710008</v>
       </c>
       <c r="G3">
-        <v>44.34324849966659</v>
+        <v>44.35078211670735</v>
       </c>
       <c r="H3">
         <v>7.105427357601002E-15</v>
       </c>
       <c r="I3">
-        <v>0.07879019120271827</v>
+        <v>0.07880357712159522</v>
       </c>
       <c r="J3">
-        <v>44.17212713936431</v>
+        <v>44.17963168404705</v>
       </c>
       <c r="K3">
-        <v>44.35465659035341</v>
+        <v>44.36219214555138</v>
       </c>
       <c r="L3">
-        <v>0.1825294509891009</v>
+        <v>0.1825604615043233</v>
       </c>
       <c r="M3">
-        <v>0.1277706156923628</v>
+        <v>0.127792323053022</v>
       </c>
       <c r="N3">
         <v>1.064148394560983</v>
       </c>
       <c r="O3">
-        <v>0.1200684193533693</v>
+        <v>0.1200888181631313</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>

--- a/outputs/Block2_2026_Target_Stability_v12.xlsx
+++ b/outputs/Block2_2026_Target_Stability_v12.xlsx
@@ -552,37 +552,37 @@
         <v>32</v>
       </c>
       <c r="E2">
-        <v>52.77257599289993</v>
+        <v>52.64302802913263</v>
       </c>
       <c r="F2">
-        <v>52.77257599289993</v>
+        <v>52.64302802913264</v>
       </c>
       <c r="G2">
-        <v>52.82421788329265</v>
+        <v>52.69454314720812</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1.4210854715202E-14</v>
       </c>
       <c r="I2">
-        <v>0.09385938937672039</v>
+        <v>0.09362898006761752</v>
       </c>
       <c r="J2">
-        <v>52.62036831595296</v>
+        <v>52.49119399691017</v>
       </c>
       <c r="K2">
-        <v>52.83780785444863</v>
+        <v>52.70809975722799</v>
       </c>
       <c r="L2">
-        <v>0.2174395384956753</v>
+        <v>0.2169057603178217</v>
       </c>
       <c r="M2">
-        <v>0.152207676946972</v>
+        <v>0.1518340322224603</v>
       </c>
       <c r="N2">
         <v>1.323492690170848</v>
       </c>
       <c r="O2">
-        <v>0.1150045467401288</v>
+        <v>0.1147222295597721</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
@@ -608,37 +608,37 @@
         <v>32</v>
       </c>
       <c r="E3">
-        <v>44.30742400710007</v>
+        <v>44.43697197086736</v>
       </c>
       <c r="F3">
-        <v>44.30742400710008</v>
+        <v>44.43697197086736</v>
       </c>
       <c r="G3">
-        <v>44.35078211670735</v>
+        <v>44.48045685279188</v>
       </c>
       <c r="H3">
-        <v>7.105427357601002E-15</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0.07880357712159522</v>
+        <v>0.07903398643070164</v>
       </c>
       <c r="J3">
-        <v>44.17963168404705</v>
+        <v>44.30880600308983</v>
       </c>
       <c r="K3">
-        <v>44.36219214555138</v>
+        <v>44.49190024277203</v>
       </c>
       <c r="L3">
-        <v>0.1825604615043233</v>
+        <v>0.1830942396821911</v>
       </c>
       <c r="M3">
-        <v>0.127792323053022</v>
+        <v>0.1281659677775266</v>
       </c>
       <c r="N3">
         <v>1.064148394560983</v>
       </c>
       <c r="O3">
-        <v>0.1200888181631313</v>
+        <v>0.1204399390466607</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>

--- a/outputs/Block2_2026_Target_Stability_v12.xlsx
+++ b/outputs/Block2_2026_Target_Stability_v12.xlsx
@@ -552,37 +552,37 @@
         <v>32</v>
       </c>
       <c r="E2">
-        <v>52.64302802913263</v>
+        <v>52.9566065934066</v>
       </c>
       <c r="F2">
-        <v>52.64302802913264</v>
+        <v>52.9566065934066</v>
       </c>
       <c r="G2">
-        <v>52.69454314720812</v>
+        <v>53.00842857142858</v>
       </c>
       <c r="H2">
-        <v>1.4210854715202E-14</v>
+        <v>7.105427357601002E-15</v>
       </c>
       <c r="I2">
-        <v>0.09362898006761752</v>
+        <v>0.09418669952721606</v>
       </c>
       <c r="J2">
-        <v>52.49119399691017</v>
+        <v>52.80386813186814</v>
       </c>
       <c r="K2">
-        <v>52.70809975722799</v>
+        <v>53.02206593406594</v>
       </c>
       <c r="L2">
-        <v>0.2169057603178217</v>
+        <v>0.2181978021978068</v>
       </c>
       <c r="M2">
-        <v>0.1518340322224603</v>
+        <v>0.1527384615384619</v>
       </c>
       <c r="N2">
         <v>1.323492690170848</v>
       </c>
       <c r="O2">
-        <v>0.1147222295597721</v>
+        <v>0.1154055951142013</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
@@ -608,37 +608,37 @@
         <v>32</v>
       </c>
       <c r="E3">
-        <v>44.43697197086736</v>
+        <v>44.1233934065934</v>
       </c>
       <c r="F3">
-        <v>44.43697197086736</v>
+        <v>44.12339340659342</v>
       </c>
       <c r="G3">
-        <v>44.48045685279188</v>
+        <v>44.16657142857143</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1.4210854715202E-14</v>
       </c>
       <c r="I3">
-        <v>0.07903398643070164</v>
+        <v>0.07847626697110505</v>
       </c>
       <c r="J3">
-        <v>44.30880600308983</v>
+        <v>43.99613186813187</v>
       </c>
       <c r="K3">
-        <v>44.49190024277203</v>
+        <v>44.17793406593407</v>
       </c>
       <c r="L3">
-        <v>0.1830942396821911</v>
+        <v>0.1818021978021989</v>
       </c>
       <c r="M3">
-        <v>0.1281659677775266</v>
+        <v>0.1272615384615321</v>
       </c>
       <c r="N3">
         <v>1.064148394560983</v>
       </c>
       <c r="O3">
-        <v>0.1204399390466607</v>
+        <v>0.1195900300296315</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>

--- a/outputs/Block2_2026_Target_Stability_v12.xlsx
+++ b/outputs/Block2_2026_Target_Stability_v12.xlsx
@@ -552,37 +552,37 @@
         <v>32</v>
       </c>
       <c r="E2">
-        <v>52.9566065934066</v>
+        <v>52.80457815565729</v>
       </c>
       <c r="F2">
-        <v>52.9566065934066</v>
+        <v>52.8045781556573</v>
       </c>
       <c r="G2">
-        <v>53.00842857142858</v>
+        <v>52.85625136254632</v>
       </c>
       <c r="H2">
         <v>7.105427357601002E-15</v>
       </c>
       <c r="I2">
-        <v>0.09418669952721606</v>
+        <v>0.09391630726254439</v>
       </c>
       <c r="J2">
-        <v>52.80386813186814</v>
+        <v>52.65227817745804</v>
       </c>
       <c r="K2">
-        <v>53.02206593406594</v>
+        <v>52.86984957488554</v>
       </c>
       <c r="L2">
-        <v>0.2181978021978068</v>
+        <v>0.2175713974275055</v>
       </c>
       <c r="M2">
-        <v>0.1527384615384619</v>
+        <v>0.1522999781992525</v>
       </c>
       <c r="N2">
         <v>1.323492690170848</v>
       </c>
       <c r="O2">
-        <v>0.1154055951142013</v>
+        <v>0.1150742873990428</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
@@ -608,37 +608,37 @@
         <v>32</v>
       </c>
       <c r="E3">
-        <v>44.1233934065934</v>
+        <v>44.27542184434272</v>
       </c>
       <c r="F3">
-        <v>44.12339340659342</v>
+        <v>44.27542184434272</v>
       </c>
       <c r="G3">
-        <v>44.16657142857143</v>
+        <v>44.31874863745368</v>
       </c>
       <c r="H3">
-        <v>1.4210854715202E-14</v>
+        <v>7.105427357601002E-15</v>
       </c>
       <c r="I3">
-        <v>0.07847626697110505</v>
+        <v>0.07874665923576957</v>
       </c>
       <c r="J3">
-        <v>43.99613186813187</v>
+        <v>44.14772182254198</v>
       </c>
       <c r="K3">
-        <v>44.17793406593407</v>
+        <v>44.33015042511447</v>
       </c>
       <c r="L3">
-        <v>0.1818021978021989</v>
+        <v>0.1824286025724859</v>
       </c>
       <c r="M3">
-        <v>0.1272615384615321</v>
+        <v>0.1277000218007345</v>
       </c>
       <c r="N3">
         <v>1.064148394560983</v>
       </c>
       <c r="O3">
-        <v>0.1195900300296315</v>
+        <v>0.1200020809629821</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
